--- a/03_GC500_Delivery_Control/buildings_charges_16Oct2026/GC500_Buildings_Charges_16Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/buildings_charges_16Oct2026/GC500_Buildings_Charges_16Oct2026.xlsx
@@ -695,15 +695,23 @@
           <t>Building 6m</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1189410</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9968862 / 93</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1426.07</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>145.74</v>
@@ -730,7 +738,13 @@
         <v>1603.78</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1603.78</v>
+        <v>3029.85</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1655.83</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>52.05</v>
       </c>
     </row>
     <row r="5">
@@ -2182,21 +2196,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1189410</t>
+          <t>1282487</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9968862 / 93</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>1426.07</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>145.74</v>
@@ -2223,13 +2234,7 @@
         <v>1603.78</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>3029.85</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>1655.83</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>52.05</v>
+        <v>1603.78</v>
       </c>
     </row>
     <row r="27">
